--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0102.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0102.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Không trọng lực thế này thì ta không điều khiển được hướng đi đâu. Chỉ toàn xoay lộn nhào thôi!</t>
+          <t>Không trọng lực thế này thì tao không điều khiển được hướng đi đâu. Chỉ toàn xoay lộn nhào thôi!</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đủ rồi đấy, đừng có mà viết tiểu thuyết mạng Huanglong nữa, và ngừng nói năng kiểu đó trước khi ta phải ra tay!</t>
+          <t>Đủ rồi đấy, đừng có mà viết tiểu thuyết mạng Huanglong nữa, và ngừng nói năng kiểu đó trước khi tao phải ra tay!</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ta không ghét đâu. Nhưng huấn luyện Đồng Bộ à? Cộng hưởng với Exostrider? Chiến đấu với bọn Threnodian? Chuyến nghiên cứu này chẳng thư giãn chút nào.</t>
+          <t>Tao không ghét đâu. Nhưng huấn luyện Đồng Bộ à? Cộng hưởng với Exostrider? Chiến đấu với bọn Threnodian? Chuyến nghiên cứu này chẳng thư giãn chút nào.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Đang trên đường à? Ta tưởng cậu đang ngáy o o trong kho như con Flufftail Fox ngủ đông ấy. Phải gọi ba lần mới tỉnh!</t>
+          <t>Đang trên đường à? Tao tưởng cậu đang ngáy o o trong kho như con Flufftail Fox ngủ đông ấy. Phải gọi ba lần mới tỉnh!</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Ta không nhận được thông báo hủy. Vậy mà "Sản phẩm Cánh Nông Nghiệp Mới" lại tự dưng bị chặn trên WavesLine của ta. Chính ngươi làm đấy, phải không?</t>
+          <t>Tao không nhận được thông báo hủy. Vậy mà "Sản phẩm Cánh Nông Nghiệp Mới" lại tự dưng bị chặn trên WavesLine của tao. Chính mày làm đấy, phải không?</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>...Ta sẽ đi tìm cái gì đó giòn tan khi cắn vào.</t>
+          <t>...Tao sẽ đi tìm cái gì đó giòn tan khi cắn vào.</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Ừ, nhưng hồi mới vào tỉ lệ của ta thấp thê thảm lắm. Phải tăng lên chứ, phải không? Dù sao vẫn còn cách xa kỷ lục cao nhất.</t>
+          <t>Ừ, nhưng hồi mới vào tỉ lệ của tao thấp thê thảm lắm. Phải tăng lên chứ, phải không? Dù sao vẫn còn cách xa kỷ lục cao nhất.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Ha. Cậu nghĩ chưa ai thử cách đó à?</t>
+          <t>Ha. Mày nghĩ chưa ai thử cách đó à?</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Hử? Ta vừa bảo cậu là cô ấy KHÔNG dễ chịu tý nào mà!</t>
+          <t>Hử? Tao vừa bảo cậu là cô ấy KHÔNG dễ chịu tý nào mà!</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Ai thèm quan tâm? Đây là cơ hội để nhận một câu đố cuộc đời do chính I.R.I.S. tạo ra! Ngươi nghĩ ta lại bỏ lỡ cơ hội này sao?!</t>
+          <t>Ai thèm quan tâm? Đây là cơ hội để nhận một câu đố cuộc đời do chính I.R.I.S. tạo ra! Mày nghĩ tao lại bỏ lỡ cơ hội này sao?!</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Ta bảo không! Trả ta cái thẻ ID đây, đồ chết tiệt!</t>
+          <t>Tao bảo không! Trả tao cái thẻ ID đây, đồ chết tiệt!</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Ta có ý hay hơn. Gia nhập Hội Học sinh đi. Giúp tụi ta củng cố an ninh mạng trong trường. Có cả tín chỉ thưởng nữa đấy!</t>
+          <t>Tao có ý hay hơn. Gia nhập Hội Học sinh đi. Giúp tụi tao củng cố an ninh mạng trong trường. Có cả tín chỉ thưởng nữa đấy!</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Này, ta vẫn cho ngươi đổi thưởng đấy. Nội quy sự kiện đâu có cấm kiếm điểm bằng "thủ thuật kỹ thuật" đâu.</t>
+          <t>Này, tao vẫn cho mày đổi thưởng đấy. Nội quy sự kiện đâu có cấm kiếm điểm bằng "thủ thuật kỹ thuật" đâu.</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Đang kích hoạt quyền quản trị... Khởi động giao thức bảo mật... Và— Ừ, được rồi. Mấy điểm này cậu không kiếm được từ trò giải đố đâu. Cậu lợi dụng lỗi phải không?</t>
+          <t>Đang kích hoạt quyền quản trị... Khởi động giao thức bảo mật... Và— Ừ, được rồi. Mấy điểm này mày không kiếm được từ trò giải đố đâu. Mày lợi dụng lỗi phải không?</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Không đâu, nhưng đừng lo. Về sửa game thì ta là dân chuyên nghiệp rồi.</t>
+          <t>Không đâu, nhưng đừng lo. Về sửa game thì tao là dân chuyên nghiệp rồi.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Được rồi, nghe ta nói này. Chúng ta cần làm lại vải cho lũ thú bông Snowfluff Seal.</t>
+          <t>Được rồi, nghe tao nói này. Chúng ta cần làm lại vải cho lũ thú bông Snowfluff Seal.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hừm. Tổ chức triển lãm văn hóa Roya dễ hơn ta tưởng...</t>
+          <t>Hừm. Tổ chức triển lãm văn hóa Roya dễ hơn tao tưởng...</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Hừm. Tổ chức triển lãm văn hóa Roya dễ hơn ta tưởng nhiều. Đủ loại học sinh Roya kéo đến giúp.</t>
+          <t>Hừm. Tổ chức triển lãm văn hóa Roya dễ hơn tao tưởng nhiều. Đủ loại học sinh Roya kéo đến giúp.</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>...Ta hỏi là ngươi đã học tư thế chưa! Ai cho phép ngươi lấy cài đặt của ta?!</t>
+          <t>...Tao hỏi là mày đã học tư thế chưa! Ai cho phép mày lấy cài đặt của tao?!</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Muốn xem tranh luận nào không? Ta thấy cái về Helios nghe khá thú vị đấy.</t>
+          <t>Muốn xem tranh luận nào không? Tao thấy cái về Helios nghe khá thú vị đấy.</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Muốn xem tranh luận nào không? Ta thấy cái về Helios nghe khá thú vị đấy.</t>
+          <t>Muốn xem tranh luận nào không? Tao thấy cái về Helios nghe khá thú vị đấy.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Giấy phép Solsworn, phê duyệt của Học viện—tất cả những thứ đó để ta lo!</t>
+          <t>Giấy phép Solsworn, phê duyệt của Học viện—tất cả những thứ đó để tao lo!</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Haha, cuối cùng cũng đến lượt ta sai khiến một con TARD-E rồi!</t>
+          <t>Haha, cuối cùng cũng đến lượt tao sai khiến một con TARD-E rồi!</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Haha, cuối cùng cũng đến lượt ta sai khiến một con TARD-E rồi!</t>
+          <t>Haha, cuối cùng cũng đến lượt tao sai khiến một con TARD-E rồi!</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>TO QUÁ ĐI MẤT! Ta muốn trọn bộ đồ Snowfluff Seal luôn. Áo, cốc, tất tần tật. Ta là fan &lt;i&gt;cuồng&lt;/i&gt; Snowfluff Seal chính hiệu!</t>
+          <t>TO QUÁ ĐI MẤT! Tao muốn trọn bộ đồ Snowfluff Seal luôn. Áo, cốc, tất tần tật. Tao là fan &lt;i&gt;cuồng&lt;/i&gt; Snowfluff Seal chính hiệu!</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Ngon! Ợ! Cho ta thêm đi! Ợ!</t>
+          <t>Ngon! Ợ! Cho tao thêm đi! Ợ!</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Ném cho ta một viên gel năng lượng đi.</t>
+          <t>Ném cho tao một viên gel năng lượng đi.</t>
         </is>
       </c>
     </row>
